--- a/data/trans_orig/P6702-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6702-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>40797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69243</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56670</t>
+          <t>56207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79681</t>
+          <t>78422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115825</t>
+          <t>116645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36273</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63933</t>
+          <t>63898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>47821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68653</t>
+          <t>68716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105164</t>
+          <t>106022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92252</t>
+          <t>90508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126456</t>
+          <t>126233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44883</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72947</t>
+          <t>72522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>144306</t>
+          <t>147182</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>189438</t>
+          <t>192835</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51168</t>
+          <t>49780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79751</t>
+          <t>77885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46185</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>76914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116517</t>
+          <t>116224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39596</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37738</t>
+          <t>36656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39855</t>
+          <t>39821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65875</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56338</t>
+          <t>56948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>29485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53331</t>
+          <t>54665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66253</t>
+          <t>67754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101723</t>
+          <t>104109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38971</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67702</t>
+          <t>67218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80033</t>
+          <t>80761</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>111757</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49403</t>
+          <t>49040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74699</t>
+          <t>76466</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136113</t>
+          <t>138168</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179678</t>
+          <t>177412</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59848</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32762</t>
+          <t>30954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52649</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84418</t>
+          <t>83873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>34096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61147</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>27648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49400</t>
+          <t>48033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82187</t>
+          <t>80291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>29478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51197</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45262</t>
+          <t>46597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>73525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42216</t>
+          <t>40835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69753</t>
+          <t>67353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55916</t>
+          <t>56968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87441</t>
+          <t>87750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79797</t>
+          <t>79598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113145</t>
+          <t>114170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43172</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>111308</t>
+          <t>110125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149045</t>
+          <t>146162</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53777</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82967</t>
+          <t>85193</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77638</t>
+          <t>78700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113375</t>
+          <t>113674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33117</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>28810</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>53518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74318</t>
+          <t>73980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108698</t>
+          <t>110316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52944</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80439</t>
+          <t>82496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137052</t>
+          <t>135172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182134</t>
+          <t>182347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52170</t>
+          <t>50513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85740</t>
+          <t>82594</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33217</t>
+          <t>32987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59157</t>
+          <t>58510</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90925</t>
+          <t>91701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>131682</t>
+          <t>131751</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109173</t>
+          <t>109494</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147893</t>
+          <t>148874</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85362</t>
+          <t>83938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117855</t>
+          <t>118692</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>204289</t>
+          <t>204659</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>255998</t>
+          <t>254630</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72267</t>
+          <t>70793</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105330</t>
+          <t>105121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74626</t>
+          <t>74357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125132</t>
+          <t>124799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>167856</t>
+          <t>167793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>40715</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67765</t>
+          <t>68463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36665</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63150</t>
+          <t>63841</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96112</t>
+          <t>99836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29537</t>
+          <t>30467</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29677</t>
+          <t>29975</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53369</t>
+          <t>53575</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47932</t>
+          <t>47554</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>77544</t>
+          <t>77135</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26138</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>62700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46174</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>69865</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42810</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>67590</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93130</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>130149</t>
+          <t>127705</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>40870</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>43145</t>
+          <t>43410</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>48157</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76317</t>
+          <t>78038</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>39511</t>
+          <t>40490</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>36211</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>215803</t>
+          <t>221141</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>277016</t>
+          <t>278286</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>181933</t>
+          <t>185941</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>239420</t>
+          <t>239292</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>418870</t>
+          <t>417761</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>501195</t>
+          <t>500646</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>185001</t>
+          <t>184924</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>242752</t>
+          <t>243459</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>127400</t>
+          <t>129838</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>175424</t>
+          <t>176047</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>326799</t>
+          <t>325279</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>400888</t>
+          <t>402008</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>453313</t>
+          <t>450519</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>523837</t>
+          <t>524092</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>280364</t>
+          <t>279662</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>342477</t>
+          <t>338623</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>748294</t>
+          <t>749166</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>841067</t>
+          <t>844814</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>265636</t>
+          <t>260722</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>326423</t>
+          <t>322644</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>148689</t>
+          <t>150072</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>198282</t>
+          <t>198857</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>425035</t>
+          <t>425479</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>505496</t>
+          <t>506485</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>153117</t>
+          <t>155447</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>204241</t>
+          <t>206271</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>84286</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>123897</t>
+          <t>125310</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>252728</t>
+          <t>251338</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>316040</t>
+          <t>317305</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43587</t>
+          <t>40645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>69921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39164</t>
+          <t>38750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65325</t>
+          <t>62840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88155</t>
+          <t>85156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123870</t>
+          <t>123529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52355</t>
+          <t>52863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80904</t>
+          <t>82067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>45745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81760</t>
+          <t>82669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118637</t>
+          <t>117923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73747</t>
+          <t>72676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105901</t>
+          <t>104138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58676</t>
+          <t>59745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>86555</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>139271</t>
+          <t>137931</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179986</t>
+          <t>181284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39087</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>66592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>29844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52604</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74249</t>
+          <t>75205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111814</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>29098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>26532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50789</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49789</t>
+          <t>50133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>43970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54586</t>
+          <t>55117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86186</t>
+          <t>84979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57789</t>
+          <t>58570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45593</t>
+          <t>45948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64007</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97800</t>
+          <t>97466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77676</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109277</t>
+          <t>108482</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46275</t>
+          <t>46420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72282</t>
+          <t>73637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134143</t>
+          <t>132291</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174453</t>
+          <t>173033</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56930</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34753</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59964</t>
+          <t>59794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72288</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106556</t>
+          <t>106532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17886</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>31307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56764</t>
+          <t>58218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42167</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43988</t>
+          <t>44674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34979</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61245</t>
+          <t>60762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71021</t>
+          <t>69926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101039</t>
+          <t>99791</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31585</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>90077</t>
+          <t>92832</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124861</t>
+          <t>124981</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65529</t>
+          <t>67780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>53581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83791</t>
+          <t>82833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>34607</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>43533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67250</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100890</t>
+          <t>101537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61507</t>
+          <t>60389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92280</t>
+          <t>91480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135143</t>
+          <t>134592</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>181319</t>
+          <t>182704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63971</t>
+          <t>64800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98914</t>
+          <t>97151</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>44983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71915</t>
+          <t>74085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118697</t>
+          <t>118721</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>161720</t>
+          <t>162270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128087</t>
+          <t>126495</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>169605</t>
+          <t>167344</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94353</t>
+          <t>92613</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>127912</t>
+          <t>127413</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>234146</t>
+          <t>231697</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>285757</t>
+          <t>284415</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101752</t>
+          <t>101908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142341</t>
+          <t>142036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69698</t>
+          <t>70020</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102807</t>
+          <t>103961</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182005</t>
+          <t>182899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231883</t>
+          <t>235399</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72112</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>52058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77423</t>
+          <t>78915</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114619</t>
+          <t>116951</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24829</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48105</t>
+          <t>47190</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29619</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>51559</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60455</t>
+          <t>58561</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>90835</t>
+          <t>91320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>45576</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>45366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53503</t>
+          <t>52950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84098</t>
+          <t>83055</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>51012</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78767</t>
+          <t>78022</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65369</t>
+          <t>66120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92957</t>
+          <t>93372</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>123181</t>
+          <t>125225</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>162485</t>
+          <t>161713</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28643</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>52428</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>57851</t>
+          <t>57985</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>87986</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32941</t>
+          <t>32224</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25461</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>49305</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>204612</t>
+          <t>204620</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>261645</t>
+          <t>262435</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>177626</t>
+          <t>178958</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>229720</t>
+          <t>231795</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>397515</t>
+          <t>400917</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>478387</t>
+          <t>476938</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>227741</t>
+          <t>227575</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>288297</t>
+          <t>285517</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>148860</t>
+          <t>148780</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>197085</t>
+          <t>197231</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>393314</t>
+          <t>394564</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>468605</t>
+          <t>470152</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>441804</t>
+          <t>439575</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>514724</t>
+          <t>513727</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>311729</t>
+          <t>313924</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>373671</t>
+          <t>375504</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>772847</t>
+          <t>771885</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>870641</t>
+          <t>865891</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>277500</t>
+          <t>275900</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>342605</t>
+          <t>341631</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>191342</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>246537</t>
+          <t>245619</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>488914</t>
+          <t>483915</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>568416</t>
+          <t>567356</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>126568</t>
+          <t>125062</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>173751</t>
+          <t>172379</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>80386</t>
+          <t>79535</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>118866</t>
+          <t>116782</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>218798</t>
+          <t>214638</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>275952</t>
+          <t>276081</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>43596</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47737</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,32 +9412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42578</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>72431</t>
+          <t>80181</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59789</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86089</t>
+          <t>94663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -9490,32 +9490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9525,32 +9525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>25145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>46726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>33276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,32 +9638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9673,32 +9673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>41469</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49414</t>
+          <t>54567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>25030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>16133</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9839,12 +9839,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>11172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28084</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>31120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41412</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>57260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -10172,69 +10172,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8386</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4759</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13486</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>20,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8217</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>13636</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>27</t>
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>33148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>25545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22070</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22786</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41486</t>
+          <t>43742</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29285</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,32 +10581,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,32 +10741,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>261169</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63628</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>301185</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,32 +10776,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,32 +10811,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>264989</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320015</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -10854,32 +10854,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10889,32 +10889,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44054</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>23344</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>157245</t>
+          <t>42669</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,32 +11002,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>41656</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>30815</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154151</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75471</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,32 +11423,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29817</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>45406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29980</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11493,32 +11493,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>58927</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40114</t>
+          <t>46177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65117</t>
+          <t>73979</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18881</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>30796</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42945</t>
+          <t>43677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48749</t>
+          <t>50341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36922</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61286</t>
+          <t>64175</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42820</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34286</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>58714</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>91569</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77837</t>
+          <t>84741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>107885</t>
+          <t>116103</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33576</t>
+          <t>37571</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>47389</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53544</t>
+          <t>61540</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>104336</t>
+          <t>116555</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>104336</t>
+          <t>116555</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>104336</t>
+          <t>116555</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>228077</t>
+          <t>251017</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>228077</t>
+          <t>251017</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>228077</t>
+          <t>251017</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,32 +12105,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,32 +12140,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12175,32 +12175,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>35333</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12331,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>46524</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,32 +12366,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>19501</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>46614</t>
+          <t>60114</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>46992</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>60126</t>
+          <t>75544</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>35435</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>38077</t>
+          <t>47193</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>28739</t>
+          <t>35282</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48945</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,32 +12592,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12627,32 +12627,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>29020</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>44597</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>358752</t>
+          <t>128898</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>170740</t>
+          <t>107908</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>542684</t>
+          <t>153140</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>92071</t>
+          <t>102691</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>76860</t>
+          <t>88186</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>106707</t>
+          <t>119780</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>450824</t>
+          <t>231589</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>259616</t>
+          <t>204763</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>740582</t>
+          <t>259036</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>61516</t>
+          <t>67098</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>51917</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>108172</t>
+          <t>88228</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>49525</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>61785</t>
+          <t>68529</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>111041</t>
+          <t>121290</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>53614</t>
+          <t>102082</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>155831</t>
+          <t>144585</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>138428</t>
+          <t>156211</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>53538</t>
+          <t>130701</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>230001</t>
+          <t>180079</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>108524</t>
+          <t>119613</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>124427</t>
+          <t>137019</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>246952</t>
+          <t>275824</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>124998</t>
+          <t>247404</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>338553</t>
+          <t>306149</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>81179</t>
+          <t>92361</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>75383</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>136513</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>68568</t>
+          <t>78270</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>56594</t>
+          <t>64409</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>82634</t>
+          <t>94623</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>149747</t>
+          <t>170631</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>69654</t>
+          <t>146406</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>207952</t>
+          <t>194622</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>33120</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>53455</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>25622</t>
+          <t>45688</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>77852</t>
+          <t>80084</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>347692</t>
+          <t>387886</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>347692</t>
+          <t>387886</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>347692</t>
+          <t>387886</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1012018</t>
+          <t>861754</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1012018</t>
+          <t>861754</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1012018</t>
+          <t>861754</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
